--- a/BWI/bestwine_output/bestwine_Cayman Islands.xlsx
+++ b/BWI/bestwine_output/bestwine_Cayman Islands.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA10"/>
+  <dimension ref="A1:AA11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1501,6 +1501,91 @@
       <c r="Z10" s="4" t="inlineStr"/>
       <c r="AA10" s="4" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Ian Boxall</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr"/>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>167896</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Cayman Islands</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>George Town</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Madison Grace</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>https://7cellars.ky</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>272169</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>info@7cellars.ky</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr"/>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61588359682237</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/7cellars.ky</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr"/>
+      <c r="V11" s="2" t="inlineStr"/>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>Ian Boxall</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>Wine Merchant</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr"/>
+      <c r="Z11" s="2" t="inlineStr"/>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ian-boxall-ab170214b/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
